--- a/site/leagues/proliga/2026_2027/xlsx/opponent_shooting_packs/opponent_shooting_pack_SLB.xlsx
+++ b/site/leagues/proliga/2026_2027/xlsx/opponent_shooting_packs/opponent_shooting_pack_SLB.xlsx
@@ -482,7 +482,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>S. Sousa (28 L)</t>
+          <t>S. Sousa (45 L)</t>
         </is>
       </c>
     </row>
@@ -494,7 +494,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>S. Sousa (14.0 3PA)</t>
+          <t>S. Sousa (21.0 3PA)</t>
         </is>
       </c>
     </row>
@@ -506,7 +506,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>M. Sousa (1.727)</t>
+          <t>M. Sousa (1.316)</t>
         </is>
       </c>
     </row>
@@ -518,7 +518,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Paint Non-RA (38 L)</t>
+          <t>Paint Non-RA (64 L)</t>
         </is>
       </c>
     </row>
@@ -530,7 +530,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Corner 3 Left (50.0%)</t>
+          <t>Corner 3 Left (54.5%)</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH6"/>
+  <dimension ref="A1:BH7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -574,7 +574,7 @@
     <col width="19" customWidth="1" min="24" max="24"/>
     <col width="16" customWidth="1" min="25" max="25"/>
     <col width="16" customWidth="1" min="26" max="26"/>
-    <col width="17" customWidth="1" min="27" max="27"/>
+    <col width="19" customWidth="1" min="27" max="27"/>
     <col width="16" customWidth="1" min="28" max="28"/>
     <col width="16" customWidth="1" min="29" max="29"/>
     <col width="22" customWidth="1" min="30" max="30"/>
@@ -592,7 +592,7 @@
     <col width="19" customWidth="1" min="42" max="42"/>
     <col width="20" customWidth="1" min="43" max="43"/>
     <col width="20" customWidth="1" min="44" max="44"/>
-    <col width="17" customWidth="1" min="45" max="45"/>
+    <col width="19" customWidth="1" min="45" max="45"/>
     <col width="20" customWidth="1" min="46" max="46"/>
     <col width="20" customWidth="1" min="47" max="47"/>
     <col width="23" customWidth="1" min="48" max="48"/>
@@ -944,172 +944,172 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H2" t="n">
+        <v>18</v>
+      </c>
+      <c r="I2" t="n">
+        <v>43</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>24</v>
+      </c>
+      <c r="L2" t="n">
         <v>11</v>
       </c>
-      <c r="I2" t="n">
-        <v>27</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>39.3%</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>14</v>
-      </c>
-      <c r="L2" t="n">
-        <v>6</v>
-      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="O2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
+          <t>53.3%</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>46.7%</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
+        <v>0.9555555555555556</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>13</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>38.5%</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>23.1%</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AB2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AE2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>38.5%</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AH2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>23.1%</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AK2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL2" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="S2" t="n">
-        <v>0.9642857142857143</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AN2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>38.5%</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="V2" t="n">
+      <c r="AQ2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>23.1%</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AT2" t="n">
         <v>8</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="Y2" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>42.9%</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="AB2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="AE2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AH2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>42.9%</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="AK2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="AN2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AQ2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>42.9%</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="AT2" t="n">
-        <v>5</v>
-      </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AV2" t="n">
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY2" t="n">
         <v>1</v>
@@ -1140,23 +1140,23 @@
         </is>
       </c>
       <c r="BC2" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="BG2" t="n">
         <v>3</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>1</v>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>300.0%</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>300.0%</t>
-        </is>
-      </c>
-      <c r="BG2" t="n">
-        <v>2</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
@@ -1196,162 +1196,172 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="H3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I3" t="n">
+        <v>23</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>31.2%</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>19</v>
+      </c>
+      <c r="L3" t="n">
+        <v>7</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>36.8%</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
         <v>13</v>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>30.0%</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
+      <c r="O3" t="n">
+        <v>3</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>23.1%</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>59.4%</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>40.6%</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>0.71875</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
         <v>13</v>
       </c>
-      <c r="L3" t="n">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>46.2%</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>22.2%</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
         <v>5</v>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>38.5%</t>
-        </is>
-      </c>
-      <c r="N3" t="n">
-        <v>7</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1</v>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>14.3%</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>65.0%</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>35.0%</t>
-        </is>
-      </c>
-      <c r="S3" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
         <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="V3" t="n">
-        <v>10</v>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="AE3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>46.2%</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="Y3" t="n">
+      <c r="AH3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>22.2%</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AK3" t="n">
         <v>5</v>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AL3" t="inlineStr">
         <is>
           <t>20.0%</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AN3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>46.2%</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AQ3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>22.2%</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
         <is>
           <t>Mid-Range</t>
         </is>
       </c>
-      <c r="AB3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AE3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="AH3" t="n">
+      <c r="AT3" t="n">
         <v>5</v>
       </c>
-      <c r="AI3" t="inlineStr">
+      <c r="AU3" t="inlineStr">
         <is>
           <t>20.0%</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AN3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="AQ3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="AT3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>0.0%</t>
         </is>
       </c>
       <c r="AV3" t="n">
@@ -1359,14 +1369,14 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>600.0%</t>
         </is>
       </c>
       <c r="AX3" t="n">
         <v>5</v>
       </c>
       <c r="AY3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
@@ -1378,14 +1388,14 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>600.0%</t>
+          <t>700.0%</t>
         </is>
       </c>
       <c r="BC3" t="n">
         <v>6</v>
       </c>
       <c r="BD3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1394,7 +1404,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>600.0%</t>
         </is>
       </c>
       <c r="BG3" t="n">
@@ -1438,81 +1448,81 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="H4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I4" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L4" t="n">
         <v>5</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="O4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
+          <t>42.3%</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>57.7%</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
+        <v>0.9615384615384616</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>12</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>50.0%</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="S4" t="n">
-        <v>0.8888888888888888</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="V4" t="n">
-        <v>7</v>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>28.6%</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="Y4" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>66.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1534,11 +1544,11 @@
         </is>
       </c>
       <c r="AE4" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1547,11 +1557,11 @@
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr"/>
@@ -1563,11 +1573,11 @@
         </is>
       </c>
       <c r="AN4" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
@@ -1576,11 +1586,11 @@
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1605,14 +1615,14 @@
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AY4" t="n">
         <v>2</v>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="BA4" t="n">
@@ -1624,27 +1634,27 @@
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BD4" t="n">
         <v>2</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
           <t>400.0%</t>
         </is>
       </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>400.0%</t>
-        </is>
-      </c>
       <c r="BG4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
     </row>
@@ -1666,126 +1676,136 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SLB_K._DOMINGUES</t>
+          <t>SLB_M._SOUSA</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>292224</t>
+          <t>254179</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>K. Domingues</t>
+          <t>M. Sousa</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I5" t="n">
+        <v>25</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>52.6%</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>8</v>
+      </c>
+      <c r="L5" t="n">
+        <v>5</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>11</v>
+      </c>
+      <c r="O5" t="n">
+        <v>5</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>45.5%</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>42.1%</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>57.9%</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>1.315789473684211</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
         <v>6</v>
       </c>
-      <c r="I5" t="n">
-        <v>12</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>46.2%</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>12</v>
-      </c>
-      <c r="L5" t="n">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AE5" t="n">
         <v>6</v>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="N5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>92.3%</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>7.7%</t>
-        </is>
-      </c>
-      <c r="S5" t="n">
-        <v>0.9230769230769231</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1</v>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="V5" t="n">
-        <v>7</v>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>28.6%</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="Y5" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t>66.7%</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="AB5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AE5" t="n">
-        <v>7</v>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>28.6%</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
       <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="inlineStr"/>
@@ -1795,37 +1815,37 @@
         </is>
       </c>
       <c r="AN5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="AQ5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="AT5" t="n">
         <v>3</v>
       </c>
-      <c r="AR5" t="inlineStr">
+      <c r="AU5" t="inlineStr">
         <is>
           <t>66.7%</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="AT5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>100.0%</t>
         </is>
       </c>
       <c r="AV5" t="n">
@@ -1833,18 +1853,18 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AY5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="BA5" t="n">
@@ -1852,31 +1872,31 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="BC5" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD5" t="n">
         <v>4</v>
       </c>
-      <c r="BD5" t="n">
-        <v>7</v>
-      </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>600.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="BG5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -1898,87 +1918,87 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SLB_M._SOUSA</t>
+          <t>SLB_K._DOMINGUES</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>254179</t>
+          <t>292224</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>M. Sousa</t>
+          <t>K. Domingues</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="H6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="L6" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>94.7%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>1.727272727272727</v>
+        <v>0.9473684210526315</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="Y6" t="n">
@@ -1986,25 +2006,35 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AE6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
           <t>33.3%</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Corner 3 Right</t>
-        </is>
-      </c>
-      <c r="AB6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr"/>
@@ -2013,20 +2043,20 @@
       <c r="AL6" t="inlineStr"/>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="AN6" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="AQ6" t="n">
@@ -2034,71 +2064,309 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AT6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="AV6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="AX6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="BA6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="BC6" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="BG6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SL Benfica</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>SLB_W._OLIVEIRA</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>W. Oliveira</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>19</v>
+      </c>
+      <c r="H7" t="n">
+        <v>6</v>
+      </c>
+      <c r="I7" t="n">
+        <v>12</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>31.6%</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>15</v>
+      </c>
+      <c r="L7" t="n">
+        <v>6</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>4</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>78.9%</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>21.1%</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>0.631578947368421</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>7</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>33.3%</t>
         </is>
       </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>Corner 3 Right</t>
-        </is>
-      </c>
-      <c r="AT6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AV6" t="n">
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AE7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AH7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AN7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AQ7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AT7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AV7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="AX7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY7" t="n">
         <v>5</v>
       </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AX6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="BA6" t="n">
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="BA7" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="BC7" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD7" t="n">
         <v>5</v>
       </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="BC6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>3</v>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="BG6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>100.0%</t>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="BG7" t="n">
+        <v>6</v>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>500.0%</t>
         </is>
       </c>
     </row>
@@ -2113,7 +2381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH6"/>
+  <dimension ref="A1:BH7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2142,7 +2410,7 @@
     <col width="19" customWidth="1" min="24" max="24"/>
     <col width="16" customWidth="1" min="25" max="25"/>
     <col width="16" customWidth="1" min="26" max="26"/>
-    <col width="17" customWidth="1" min="27" max="27"/>
+    <col width="19" customWidth="1" min="27" max="27"/>
     <col width="16" customWidth="1" min="28" max="28"/>
     <col width="16" customWidth="1" min="29" max="29"/>
     <col width="22" customWidth="1" min="30" max="30"/>
@@ -2160,7 +2428,7 @@
     <col width="19" customWidth="1" min="42" max="42"/>
     <col width="20" customWidth="1" min="43" max="43"/>
     <col width="20" customWidth="1" min="44" max="44"/>
-    <col width="17" customWidth="1" min="45" max="45"/>
+    <col width="19" customWidth="1" min="45" max="45"/>
     <col width="20" customWidth="1" min="46" max="46"/>
     <col width="20" customWidth="1" min="47" max="47"/>
     <col width="23" customWidth="1" min="48" max="48"/>
@@ -2512,180 +2780,200 @@
         </is>
       </c>
       <c r="G2" t="n">
+        <v>19</v>
+      </c>
+      <c r="H2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>52.6%</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>8</v>
+      </c>
+      <c r="L2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
         <v>11</v>
-      </c>
-      <c r="H2" t="n">
-        <v>7</v>
-      </c>
-      <c r="I2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>63.6%</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>3</v>
-      </c>
-      <c r="L2" t="n">
-        <v>2</v>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="N2" t="n">
-        <v>8</v>
       </c>
       <c r="O2" t="n">
         <v>5</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>42.1%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>1.727272727272727</v>
+        <v>1.315789473684211</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>6</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
           <t>Corner 3 Left</t>
         </is>
       </c>
-      <c r="V2" t="n">
+      <c r="AB2" t="n">
         <v>3</v>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>66.7%</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AE2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="Y2" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Corner 3 Right</t>
-        </is>
-      </c>
-      <c r="AB2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
+      <c r="AH2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
       <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="inlineStr">
         <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AN2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AQ2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
           <t>Corner 3 Left</t>
         </is>
       </c>
-      <c r="AN2" t="n">
+      <c r="AT2" t="n">
         <v>3</v>
       </c>
-      <c r="AO2" t="inlineStr">
+      <c r="AU2" t="inlineStr">
         <is>
           <t>66.7%</t>
         </is>
       </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="AQ2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>Corner 3 Right</t>
-        </is>
-      </c>
-      <c r="AT2" t="n">
+      <c r="AV2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AX2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="BA2" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="BC2" t="n">
         <v>2</v>
       </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AV2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AX2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="BA2" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>1</v>
-      </c>
       <c r="BD2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -2720,201 +3008,191 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SLB_S._SOUSA</t>
+          <t>SLB_J._MENDES</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>224422</t>
+          <t>217315</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>S. Sousa</t>
+          <t>J. Mendes</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H3" t="n">
+        <v>10</v>
+      </c>
+      <c r="I3" t="n">
+        <v>25</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>38.5%</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
         <v>11</v>
       </c>
-      <c r="I3" t="n">
-        <v>27</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>39.3%</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>14</v>
-      </c>
       <c r="L3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O3" t="n">
         <v>5</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
+          <t>42.3%</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>57.7%</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>0.9615384615384616</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>12</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AE3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AH3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI3" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="S3" t="n">
-        <v>0.9642857142857143</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="V3" t="n">
+      <c r="AN3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AQ3" t="n">
         <v>8</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="Y3" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>42.9%</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
         <is>
           <t>Mid-Range</t>
         </is>
       </c>
-      <c r="AB3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="AE3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AH3" t="n">
-        <v>7</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>42.9%</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="AK3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="AN3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AQ3" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>42.9%</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
       <c r="AT3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AV3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
       <c r="AX3" t="n">
         <v>2</v>
       </c>
       <c r="AY3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
@@ -2922,18 +3200,18 @@
         </is>
       </c>
       <c r="BA3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>400.0%</t>
+          <t>500.0%</t>
         </is>
       </c>
       <c r="BC3" t="n">
         <v>3</v>
       </c>
       <c r="BD3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -2942,7 +3220,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
       <c r="BG3" t="n">
@@ -2972,209 +3250,229 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SLB_K._DOMINGUES</t>
+          <t>SLB_S._SOUSA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>292224</t>
+          <t>224422</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>K. Domingues</t>
+          <t>S. Sousa</t>
         </is>
       </c>
       <c r="G4" t="n">
+        <v>45</v>
+      </c>
+      <c r="H4" t="n">
+        <v>18</v>
+      </c>
+      <c r="I4" t="n">
+        <v>43</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>24</v>
+      </c>
+      <c r="L4" t="n">
+        <v>11</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>45.8%</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>21</v>
+      </c>
+      <c r="O4" t="n">
+        <v>7</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>53.3%</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>46.7%</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
+        <v>0.9555555555555556</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
         <v>13</v>
       </c>
-      <c r="H4" t="n">
-        <v>6</v>
-      </c>
-      <c r="I4" t="n">
-        <v>12</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>46.2%</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>12</v>
-      </c>
-      <c r="L4" t="n">
-        <v>6</v>
-      </c>
-      <c r="M4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>38.5%</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>23.1%</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC4" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="N4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>92.3%</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>7.7%</t>
-        </is>
-      </c>
-      <c r="S4" t="n">
-        <v>0.9230769230769231</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="V4" t="n">
-        <v>7</v>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>28.6%</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="AE4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>38.5%</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>23.1%</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
         <is>
           <t>Mid-Range</t>
         </is>
       </c>
-      <c r="Y4" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="AB4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AK4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
         <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="AE4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>28.6%</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
       <c r="AN4" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AQ4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>23.1%</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
           <t>Mid-Range</t>
         </is>
       </c>
-      <c r="AQ4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
       <c r="AT4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AV4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="AX4" t="n">
         <v>3</v>
       </c>
       <c r="AY4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="BA4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
       <c r="BC4" t="n">
         <v>4</v>
       </c>
       <c r="BD4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>600.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="BG4" t="n">
@@ -3182,7 +3480,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
     </row>
@@ -3204,95 +3502,95 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SLB_J._MENDES</t>
+          <t>SLB_K._DOMINGUES</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>217315</t>
+          <t>292224</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>J. Mendes</t>
+          <t>K. Domingues</t>
         </is>
       </c>
       <c r="G5" t="n">
+        <v>19</v>
+      </c>
+      <c r="H5" t="n">
+        <v>9</v>
+      </c>
+      <c r="I5" t="n">
         <v>18</v>
       </c>
-      <c r="H5" t="n">
-        <v>7</v>
-      </c>
-      <c r="I5" t="n">
-        <v>16</v>
-      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="K5" t="n">
+        <v>18</v>
+      </c>
+      <c r="L5" t="n">
         <v>9</v>
       </c>
-      <c r="L5" t="n">
-        <v>5</v>
-      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>94.7%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.9473684210526315</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="Y5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -3305,62 +3603,52 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AE5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
           <t>33.3%</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="AE5" t="n">
-        <v>7</v>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>28.6%</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AH5" t="n">
-        <v>6</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="AN5" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -3373,50 +3661,50 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AV5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>400.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="AX5" t="n">
         <v>4</v>
       </c>
       <c r="AY5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="BA5" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
           <t>300.0%</t>
-        </is>
-      </c>
-      <c r="BA5" t="n">
-        <v>3</v>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>500.0%</t>
         </is>
       </c>
       <c r="BC5" t="n">
         <v>5</v>
       </c>
       <c r="BD5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>400.0%</t>
+          <t>600.0%</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>400.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="BG5" t="n">
@@ -3424,7 +3712,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>500.0%</t>
         </is>
       </c>
     </row>
@@ -3460,162 +3748,172 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="H6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I6" t="n">
+        <v>23</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>31.2%</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>19</v>
+      </c>
+      <c r="L6" t="n">
+        <v>7</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>36.8%</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
         <v>13</v>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>30.0%</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
+      <c r="O6" t="n">
+        <v>3</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>23.1%</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>59.4%</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>40.6%</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v>0.71875</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
         <v>13</v>
       </c>
-      <c r="L6" t="n">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>46.2%</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>22.2%</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
         <v>5</v>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>38.5%</t>
-        </is>
-      </c>
-      <c r="N6" t="n">
-        <v>7</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>14.3%</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>65.0%</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>35.0%</t>
-        </is>
-      </c>
-      <c r="S6" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
         <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="V6" t="n">
-        <v>10</v>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="AE6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>46.2%</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="Y6" t="n">
+      <c r="AH6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>22.2%</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AK6" t="n">
         <v>5</v>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AL6" t="inlineStr">
         <is>
           <t>20.0%</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AN6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>46.2%</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AQ6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>22.2%</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
         <is>
           <t>Mid-Range</t>
         </is>
       </c>
-      <c r="AB6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AE6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="AH6" t="n">
+      <c r="AT6" t="n">
         <v>5</v>
       </c>
-      <c r="AI6" t="inlineStr">
+      <c r="AU6" t="inlineStr">
         <is>
           <t>20.0%</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr"/>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AN6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="AQ6" t="n">
-        <v>5</v>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="AT6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>0.0%</t>
         </is>
       </c>
       <c r="AV6" t="n">
@@ -3623,14 +3921,14 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>600.0%</t>
         </is>
       </c>
       <c r="AX6" t="n">
         <v>5</v>
       </c>
       <c r="AY6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
@@ -3642,14 +3940,14 @@
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>600.0%</t>
+          <t>700.0%</t>
         </is>
       </c>
       <c r="BC6" t="n">
         <v>6</v>
       </c>
       <c r="BD6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3658,7 +3956,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>600.0%</t>
         </is>
       </c>
       <c r="BG6" t="n">
@@ -3667,6 +3965,244 @@
       <c r="BH6" t="inlineStr">
         <is>
           <t>400.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SL Benfica</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>SLB_W._OLIVEIRA</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>W. Oliveira</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>19</v>
+      </c>
+      <c r="H7" t="n">
+        <v>6</v>
+      </c>
+      <c r="I7" t="n">
+        <v>12</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>31.6%</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>15</v>
+      </c>
+      <c r="L7" t="n">
+        <v>6</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>4</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>78.9%</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>21.1%</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>0.631578947368421</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>7</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AE7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AH7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AN7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AQ7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AT7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AV7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="AX7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="BA7" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="BC7" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="BG7" t="n">
+        <v>6</v>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>500.0%</t>
         </is>
       </c>
     </row>
@@ -3681,7 +4217,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH6"/>
+  <dimension ref="A1:BH7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3710,7 +4246,7 @@
     <col width="19" customWidth="1" min="24" max="24"/>
     <col width="16" customWidth="1" min="25" max="25"/>
     <col width="16" customWidth="1" min="26" max="26"/>
-    <col width="17" customWidth="1" min="27" max="27"/>
+    <col width="19" customWidth="1" min="27" max="27"/>
     <col width="16" customWidth="1" min="28" max="28"/>
     <col width="16" customWidth="1" min="29" max="29"/>
     <col width="22" customWidth="1" min="30" max="30"/>
@@ -3728,7 +4264,7 @@
     <col width="19" customWidth="1" min="42" max="42"/>
     <col width="20" customWidth="1" min="43" max="43"/>
     <col width="20" customWidth="1" min="44" max="44"/>
-    <col width="17" customWidth="1" min="45" max="45"/>
+    <col width="19" customWidth="1" min="45" max="45"/>
     <col width="20" customWidth="1" min="46" max="46"/>
     <col width="20" customWidth="1" min="47" max="47"/>
     <col width="23" customWidth="1" min="48" max="48"/>
@@ -4080,172 +4616,172 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H2" t="n">
+        <v>18</v>
+      </c>
+      <c r="I2" t="n">
+        <v>43</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>24</v>
+      </c>
+      <c r="L2" t="n">
         <v>11</v>
       </c>
-      <c r="I2" t="n">
-        <v>27</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>39.3%</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>14</v>
-      </c>
-      <c r="L2" t="n">
-        <v>6</v>
-      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="O2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
+          <t>53.3%</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>46.7%</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
+        <v>0.9555555555555556</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>13</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>38.5%</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>23.1%</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AB2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AE2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>38.5%</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AH2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>23.1%</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AK2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL2" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="S2" t="n">
-        <v>0.9642857142857143</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AN2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>38.5%</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="V2" t="n">
+      <c r="AQ2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>23.1%</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AT2" t="n">
         <v>8</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="Y2" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>42.9%</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="AB2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="AE2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AH2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>42.9%</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="AK2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="AN2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AQ2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>42.9%</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="AT2" t="n">
-        <v>5</v>
-      </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AV2" t="n">
@@ -4257,7 +4793,7 @@
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY2" t="n">
         <v>1</v>
@@ -4276,23 +4812,23 @@
         </is>
       </c>
       <c r="BC2" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="BG2" t="n">
         <v>3</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>1</v>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>300.0%</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>300.0%</t>
-        </is>
-      </c>
-      <c r="BG2" t="n">
-        <v>2</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
@@ -4332,81 +4868,81 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="H3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I3" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L3" t="n">
         <v>5</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="O3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
+          <t>42.3%</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>57.7%</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>0.9615384615384616</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>12</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>50.0%</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="S3" t="n">
-        <v>0.8888888888888888</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="V3" t="n">
-        <v>7</v>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>28.6%</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="Y3" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>66.7%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -4428,11 +4964,11 @@
         </is>
       </c>
       <c r="AE3" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -4441,11 +4977,11 @@
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr"/>
@@ -4457,11 +4993,11 @@
         </is>
       </c>
       <c r="AN3" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
@@ -4470,11 +5006,11 @@
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -4499,14 +5035,14 @@
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AY3" t="n">
         <v>2</v>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="BA3" t="n">
@@ -4518,27 +5054,27 @@
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BD3" t="n">
         <v>2</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
           <t>400.0%</t>
         </is>
       </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>400.0%</t>
-        </is>
-      </c>
       <c r="BG3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
     </row>
@@ -4560,207 +5096,237 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SLB_M._SOUSA</t>
+          <t>SLB_T._FILIPE</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>254179</t>
+          <t>222661</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>M. Sousa</t>
+          <t>T. Filipe</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="H4" t="n">
+        <v>10</v>
+      </c>
+      <c r="I4" t="n">
+        <v>23</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>31.2%</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>19</v>
+      </c>
+      <c r="L4" t="n">
         <v>7</v>
       </c>
-      <c r="I4" t="n">
-        <v>19</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>63.6%</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>36.8%</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>13</v>
+      </c>
+      <c r="O4" t="n">
         <v>3</v>
       </c>
-      <c r="L4" t="n">
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>23.1%</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>59.4%</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>40.6%</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
+        <v>0.71875</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>13</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>46.2%</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>22.2%</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AE4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>46.2%</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>22.2%</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AK4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AN4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>46.2%</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AQ4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>22.2%</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AT4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="AV4" t="n">
         <v>2</v>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="N4" t="n">
-        <v>8</v>
-      </c>
-      <c r="O4" t="n">
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="AX4" t="n">
         <v>5</v>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>27.3%</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>72.7%</t>
-        </is>
-      </c>
-      <c r="S4" t="n">
-        <v>1.727272727272727</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="V4" t="n">
-        <v>3</v>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="Y4" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Corner 3 Right</t>
-        </is>
-      </c>
-      <c r="AB4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="AN4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="AQ4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>Corner 3 Right</t>
-        </is>
-      </c>
-      <c r="AT4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AV4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AX4" t="n">
-        <v>1</v>
       </c>
       <c r="AY4" t="n">
         <v>3</v>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
       <c r="BA4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>700.0%</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="BD4" t="n">
         <v>3</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>500.0%</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>600.0%</t>
         </is>
       </c>
       <c r="BG4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
     </row>
@@ -4782,67 +5348,67 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SLB_T._FILIPE</t>
+          <t>SLB_M._SOUSA</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>222661</t>
+          <t>254179</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>T. Filipe</t>
+          <t>M. Sousa</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I5" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L5" t="n">
         <v>5</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>42.1%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>0.65</v>
+        <v>1.315789473684211</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
@@ -4853,11 +5419,11 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -4875,15 +5441,15 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -4892,11 +5458,11 @@
         </is>
       </c>
       <c r="AE5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -4921,11 +5487,11 @@
         </is>
       </c>
       <c r="AN5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
@@ -4943,66 +5509,66 @@
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AV5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AY5" t="n">
         <v>4</v>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>400.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="BA5" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="BC5" t="n">
         <v>2</v>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>600.0%</t>
-        </is>
-      </c>
-      <c r="BC5" t="n">
-        <v>6</v>
       </c>
       <c r="BD5" t="n">
         <v>4</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="BG5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>400.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -5024,21 +5590,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SLB_K._DOMINGUES</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>292224</t>
-        </is>
-      </c>
+          <t>SLB_W._OLIVEIRA</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>K. Domingues</t>
+          <t>W. Oliveira</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H6" t="n">
         <v>6</v>
@@ -5048,22 +5610,22 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L6" t="n">
         <v>6</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -5075,23 +5637,23 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>92.3%</t>
+          <t>78.9%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>0.9230769230769231</v>
+        <v>0.631578947368421</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="V6" t="n">
@@ -5099,38 +5661,38 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
           <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="Y6" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="AB6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="AE6" t="n">
@@ -5138,18 +5700,28 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>28.6%</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AH6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
       <c r="AJ6" t="inlineStr"/>
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="inlineStr"/>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="AN6" t="n">
@@ -5157,33 +5729,33 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AV6" t="n">
@@ -5191,14 +5763,14 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>500.0%</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AY6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
@@ -5210,29 +5782,261 @@
       </c>
       <c r="BB6" t="inlineStr">
         <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="BC6" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="BG6" t="n">
+        <v>6</v>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SL Benfica</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>SLB_K._DOMINGUES</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>292224</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>K. Domingues</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>19</v>
+      </c>
+      <c r="H7" t="n">
+        <v>9</v>
+      </c>
+      <c r="I7" t="n">
+        <v>18</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>47.4%</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>18</v>
+      </c>
+      <c r="L7" t="n">
+        <v>9</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>94.7%</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>5.3%</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>0.9473684210526315</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>12</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AE7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AN7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AQ7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AT7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="AV7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="AX7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="BA7" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
           <t>300.0%</t>
         </is>
       </c>
-      <c r="BC6" t="n">
+      <c r="BC7" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="BG7" t="n">
         <v>4</v>
       </c>
-      <c r="BD6" t="n">
-        <v>7</v>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>600.0%</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>200.0%</t>
-        </is>
-      </c>
-      <c r="BG6" t="n">
-        <v>3</v>
-      </c>
-      <c r="BH6" t="inlineStr">
+      <c r="BH7" t="inlineStr">
         <is>
           <t>500.0%</t>
         </is>
@@ -5249,13 +6053,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH2"/>
+  <dimension ref="A1:BH5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
@@ -5275,10 +6079,10 @@
     <col width="19" customWidth="1" min="21" max="21"/>
     <col width="16" customWidth="1" min="22" max="22"/>
     <col width="16" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="19" customWidth="1" min="24" max="24"/>
     <col width="16" customWidth="1" min="25" max="25"/>
     <col width="16" customWidth="1" min="26" max="26"/>
-    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="15" customWidth="1" min="27" max="27"/>
     <col width="16" customWidth="1" min="28" max="28"/>
     <col width="16" customWidth="1" min="29" max="29"/>
     <col width="22" customWidth="1" min="30" max="30"/>
@@ -5293,7 +6097,7 @@
     <col width="19" customWidth="1" min="39" max="39"/>
     <col width="20" customWidth="1" min="40" max="40"/>
     <col width="20" customWidth="1" min="41" max="41"/>
-    <col width="16" customWidth="1" min="42" max="42"/>
+    <col width="19" customWidth="1" min="42" max="42"/>
     <col width="20" customWidth="1" min="43" max="43"/>
     <col width="20" customWidth="1" min="44" max="44"/>
     <col width="16" customWidth="1" min="45" max="45"/>
@@ -5634,237 +6438,973 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SLB_S._SOUSA</t>
+          <t>SLB_M._SOUSA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>224422</t>
+          <t>254179</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>S. Sousa</t>
+          <t>M. Sousa</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="H2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>52.6%</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>8</v>
+      </c>
+      <c r="L2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
         <v>11</v>
-      </c>
-      <c r="I2" t="n">
-        <v>27</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>39.3%</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>14</v>
-      </c>
-      <c r="L2" t="n">
-        <v>6</v>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>42.9%</t>
-        </is>
-      </c>
-      <c r="N2" t="n">
-        <v>14</v>
       </c>
       <c r="O2" t="n">
         <v>5</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
+          <t>42.1%</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>57.9%</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
+        <v>1.315789473684211</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>6</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="AB2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AE2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AH2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AN2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AQ2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="AT2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="AV2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AX2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="BA2" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="BC2" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="BG2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SL Benfica</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>SLB_S._SOUSA</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>224422</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>S. Sousa</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>45</v>
+      </c>
+      <c r="H3" t="n">
+        <v>18</v>
+      </c>
+      <c r="I3" t="n">
+        <v>43</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>24</v>
+      </c>
+      <c r="L3" t="n">
+        <v>11</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>45.8%</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>21</v>
+      </c>
+      <c r="O3" t="n">
+        <v>7</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>53.3%</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>46.7%</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>0.9555555555555556</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>13</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>38.5%</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>23.1%</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AE3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>38.5%</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AH3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>23.1%</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AK3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL3" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="S2" t="n">
-        <v>0.9642857142857143</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AN3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>38.5%</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="V2" t="n">
+      <c r="AQ3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>23.1%</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AT3" t="n">
         <v>8</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AV3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="AX3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="BA3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="BC3" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="BG3" t="n">
+        <v>3</v>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SL Benfica</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>SLB_J._MENDES</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>217315</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>J. Mendes</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>26</v>
+      </c>
+      <c r="H4" t="n">
+        <v>10</v>
+      </c>
+      <c r="I4" t="n">
+        <v>25</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>38.5%</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>11</v>
+      </c>
+      <c r="L4" t="n">
+        <v>5</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>45.5%</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>15</v>
+      </c>
+      <c r="O4" t="n">
+        <v>5</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>42.3%</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>57.7%</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
+        <v>0.9615384615384616</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>12</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="Y4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AE4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AN4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AQ4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AT4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="AV4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="AX4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="BA4" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="BC4" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="BG4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SL Benfica</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>SLB_T._FILIPE</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>222661</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>T. Filipe</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>32</v>
+      </c>
+      <c r="H5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I5" t="n">
+        <v>23</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>31.2%</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>19</v>
+      </c>
+      <c r="L5" t="n">
         <v>7</v>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>42.9%</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>36.8%</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>13</v>
+      </c>
+      <c r="O5" t="n">
+        <v>3</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>23.1%</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>59.4%</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>40.6%</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>0.71875</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>13</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>46.2%</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>22.2%</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Mid-Range</t>
         </is>
       </c>
-      <c r="AB2" t="n">
+      <c r="AB5" t="n">
         <v>5</v>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>20.0%</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AE5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>46.2%</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="AE2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AH5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>22.2%</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AK5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
         <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="AH2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>42.9%</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
+      <c r="AN5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>46.2%</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AQ5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>22.2%</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
         <is>
           <t>Mid-Range</t>
         </is>
       </c>
-      <c r="AK2" t="n">
+      <c r="AT5" t="n">
         <v>5</v>
       </c>
-      <c r="AL2" t="inlineStr">
+      <c r="AU5" t="inlineStr">
         <is>
           <t>20.0%</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="AN2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AQ2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>42.9%</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="AT2" t="n">
+      <c r="AV5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="AX5" t="n">
         <v>5</v>
       </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="AV2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>300.0%</t>
-        </is>
-      </c>
-      <c r="AX2" t="n">
+      <c r="AY5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="BA5" t="n">
         <v>2</v>
       </c>
-      <c r="AY2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>200.0%</t>
-        </is>
-      </c>
-      <c r="BA2" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB2" t="inlineStr">
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>700.0%</t>
+        </is>
+      </c>
+      <c r="BC5" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="BG5" t="n">
+        <v>5</v>
+      </c>
+      <c r="BH5" t="inlineStr">
         <is>
           <t>400.0%</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>3</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>1</v>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>300.0%</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>300.0%</t>
-        </is>
-      </c>
-      <c r="BG2" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>200.0%</t>
         </is>
       </c>
     </row>
@@ -6034,27 +7574,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="F2" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="G2" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>42.1%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>0.8421052631578947</v>
+        <v>0.78125</v>
       </c>
       <c r="J2" t="n">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="K2" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -6064,7 +7604,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="O2" t="n">
@@ -6083,7 +7623,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>400.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="T2" t="n">
@@ -6117,21 +7657,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="F3" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G3" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.6428571428571429</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -6140,14 +7680,14 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="M3" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="O3" t="n">
@@ -6158,7 +7698,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>400.0%</t>
+          <t>500.0%</t>
         </is>
       </c>
       <c r="R3" t="n">
@@ -6174,7 +7714,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>400.0%</t>
+          <t>500.0%</t>
         </is>
       </c>
     </row>
@@ -6200,27 +7740,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G4" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="J4" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="K4" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -6230,7 +7770,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="O4" t="n">
@@ -6249,7 +7789,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
       <c r="T4" t="n">
@@ -6279,25 +7819,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Corner 3 Right</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -6306,14 +7846,14 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="O5" t="n">
@@ -6324,7 +7864,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
       <c r="R5" t="n">
@@ -6332,7 +7872,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>500.0%</t>
         </is>
       </c>
       <c r="T5" t="n">
@@ -6340,7 +7880,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
     </row>
@@ -6362,37 +7902,37 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G6" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.428571428571429</v>
+        <v>1.636363636363636</v>
       </c>
       <c r="J6" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -6400,7 +7940,7 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6" t="n">
         <v>5</v>
@@ -6415,11 +7955,17 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="T6" t="n">
+        <v>5</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6439,60 +7985,60 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Corner 3 Right</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G7" t="n">
+        <v>12</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="J7" t="n">
         <v>9</v>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>42.9%</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>1.285714285714286</v>
-      </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
+        <v>6</v>
+      </c>
+      <c r="L7" t="n">
         <v>0</v>
       </c>
-      <c r="K7" t="n">
+      <c r="M7" t="n">
         <v>0</v>
       </c>
-      <c r="L7" t="n">
-        <v>7</v>
-      </c>
-      <c r="M7" t="n">
-        <v>3</v>
-      </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>5.2%</t>
         </is>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="R7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
@@ -6509,7 +8055,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U5"/>
+  <dimension ref="A1:U6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6664,21 +8210,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.5</v>
+        <v>1.636363636363636</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -6687,29 +8233,29 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M2" t="n">
+        <v>6</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>6.4%</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P2" t="n">
         <v>5</v>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>9.1%</t>
-        </is>
-      </c>
-      <c r="O2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P2" t="n">
-        <v>4</v>
-      </c>
       <c r="Q2" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
       <c r="R2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -6717,7 +8263,7 @@
         </is>
       </c>
       <c r="T2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -6747,27 +8293,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="F3" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="G3" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>42.1%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.8421052631578947</v>
+        <v>0.78125</v>
       </c>
       <c r="J3" t="n">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="K3" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -6777,7 +8323,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="O3" t="n">
@@ -6796,7 +8342,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>400.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="T3" t="n">
@@ -6830,27 +8376,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G4" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="J4" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="K4" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -6860,7 +8406,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="O4" t="n">
@@ -6879,7 +8425,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
       <c r="T4" t="n">
@@ -6909,25 +8455,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Corner 3 Right</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.6428571428571429</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -6936,41 +8482,124 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="M5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="O5" t="n">
         <v>1</v>
       </c>
       <c r="P5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>4</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SL Benfica</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>45</v>
+      </c>
+      <c r="F6" t="n">
+        <v>11</v>
+      </c>
+      <c r="G6" t="n">
+        <v>33</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>24.4%</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0.7333333333333333</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>45</v>
+      </c>
+      <c r="M6" t="n">
+        <v>11</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>26.0%</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" t="n">
         <v>2</v>
       </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>400.0%</t>
-        </is>
-      </c>
-      <c r="R5" t="n">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
         <v>2</v>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>600.0%</t>
         </is>
       </c>
-      <c r="T5" t="n">
+      <c r="T6" t="n">
         <v>2</v>
       </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>400.0%</t>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>500.0%</t>
         </is>
       </c>
     </row>
@@ -6980,6 +8609,1434 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="23" customWidth="1" min="18" max="18"/>
+    <col width="28" customWidth="1" min="19" max="19"/>
+    <col width="25" customWidth="1" min="20" max="20"/>
+    <col width="32" customWidth="1" min="21" max="21"/>
+    <col width="29" customWidth="1" min="22" max="22"/>
+    <col width="38" customWidth="1" min="23" max="23"/>
+    <col width="35" customWidth="1" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>team_name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>team_code</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>team_key</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>player_id</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>global_player_id</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>player_name</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>zone</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>attempts</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>made</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>points</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>fg_pct</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>pps</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>fg2a</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>fg2m</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>fg3a</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>fg3m</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>zone_share</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>eligible_zone_profile</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>player_zone_rank_by_volume</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>player_zone_rank_by_pct</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>player_zone_rank_by_volume_all</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>player_zone_rank_by_pct_all</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>player_zone_rank_by_volume_qualified</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>player_zone_rank_by_pct_qualified</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>SL Benfica</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>SLB_T._FILIPE</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>222661</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>T. Filipe</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>13</v>
+      </c>
+      <c r="I2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J2" t="n">
+        <v>12</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>46.2%</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="M2" t="n">
+        <v>13</v>
+      </c>
+      <c r="N2" t="n">
+        <v>6</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>40.6%</t>
+        </is>
+      </c>
+      <c r="R2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SL Benfica</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>SLB_S._SOUSA</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>224422</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>S. Sousa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>13</v>
+      </c>
+      <c r="I3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J3" t="n">
+        <v>10</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>38.5%</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>0.7692307692307693</v>
+      </c>
+      <c r="M3" t="n">
+        <v>13</v>
+      </c>
+      <c r="N3" t="n">
+        <v>5</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>28.9%</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="W3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SL Benfica</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>SLB_S._SOUSA</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>224422</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>S. Sousa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>13</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J4" t="n">
+        <v>9</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>23.1%</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>0.6923076923076923</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>13</v>
+      </c>
+      <c r="P4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>28.9%</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="W4" t="n">
+        <v>1</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SL Benfica</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>SLB_J._MENDES</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>217315</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>J. Mendes</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="n">
+        <v>5</v>
+      </c>
+      <c r="J5" t="n">
+        <v>15</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>12</v>
+      </c>
+      <c r="P5" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>46.2%</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="W5" t="n">
+        <v>1</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SL Benfica</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>SLB_K._DOMINGUES</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>292224</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>K. Domingues</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J6" t="n">
+        <v>8</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="M6" t="n">
+        <v>12</v>
+      </c>
+      <c r="N6" t="n">
+        <v>4</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>63.2%</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="W6" t="n">
+        <v>1</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SL Benfica</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>SLB_T._FILIPE</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>222661</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>T. Filipe</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>9</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>6</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>22.2%</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>9</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>28.1%</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="W7" t="n">
+        <v>2</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SL Benfica</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>SLB_J._MENDES</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>217315</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>J. Mendes</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>8</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4</v>
+      </c>
+      <c r="J8" t="n">
+        <v>8</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>8</v>
+      </c>
+      <c r="N8" t="n">
+        <v>4</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>30.8%</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="W8" t="n">
+        <v>2</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SL Benfica</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>SLB_S._SOUSA</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>224422</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>S. Sousa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>8</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J9" t="n">
+        <v>8</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>8</v>
+      </c>
+      <c r="N9" t="n">
+        <v>4</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>17.8%</t>
+        </is>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="U9" t="n">
+        <v>3</v>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="W9" t="n">
+        <v>3</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SL Benfica</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>SLB_W._OLIVEIRA</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>W. Oliveira</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>7</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3</v>
+      </c>
+      <c r="J10" t="n">
+        <v>6</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="M10" t="n">
+        <v>7</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>36.8%</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="W10" t="n">
+        <v>1</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SL Benfica</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>SLB_M._SOUSA</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>254179</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>M. Sousa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>6</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4</v>
+      </c>
+      <c r="J11" t="n">
+        <v>8</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="M11" t="n">
+        <v>6</v>
+      </c>
+      <c r="N11" t="n">
+        <v>4</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>31.6%</t>
+        </is>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="W11" t="n">
+        <v>1</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SL Benfica</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>SLB_W._OLIVEIRA</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>W. Oliveira</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>6</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="M12" t="n">
+        <v>6</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>31.6%</t>
+        </is>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="W12" t="n">
+        <v>2</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SL Benfica</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>SLB_M._SOUSA</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>254179</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>M. Sousa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>5</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>5</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>26.3%</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="W13" t="n">
+        <v>2</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SL Benfica</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>SLB_T._FILIPE</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>222661</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>T. Filipe</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>5</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M14" t="n">
+        <v>5</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>15.6%</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="U14" t="n">
+        <v>3</v>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="W14" t="n">
+        <v>3</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7154,17 +10211,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SLB_T._FILIPE</t>
+          <t>SLB_J._MENDES</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>222661</t>
+          <t>217315</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>T. Filipe</t>
+          <t>J. Mendes</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -7173,13 +10230,13 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -7190,10 +10247,10 @@
         <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -7203,14 +10260,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="R2" t="n">
         <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -7218,7 +10275,7 @@
         </is>
       </c>
       <c r="U2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -7226,7 +10283,7 @@
         </is>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -7267,68 +10324,68 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="H3" t="n">
         <v>8</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
+        <v>8</v>
+      </c>
+      <c r="N3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="N3" t="n">
+      <c r="P3" t="n">
         <v>0</v>
       </c>
-      <c r="O3" t="n">
-        <v>8</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2</v>
-      </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="R3" t="n">
         <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="U3" t="n">
+        <v>3</v>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
           <t>200.0%</t>
         </is>
       </c>
-      <c r="U3" t="n">
-        <v>1</v>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>500.0%</t>
-        </is>
-      </c>
       <c r="W3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -7350,17 +10407,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SLB_S._SOUSA</t>
+          <t>SLB_T._FILIPE</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>224422</t>
+          <t>222661</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>S. Sousa</t>
+          <t>T. Filipe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -7369,27 +10426,27 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J4" t="n">
+        <v>12</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>46.2%</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="M4" t="n">
+        <v>13</v>
+      </c>
+      <c r="N4" t="n">
         <v>6</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>42.9%</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>0.8571428571428571</v>
-      </c>
-      <c r="M4" t="n">
-        <v>7</v>
-      </c>
-      <c r="N4" t="n">
-        <v>3</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -7399,14 +10456,14 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="R4" t="n">
         <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -7414,15 +10471,15 @@
         </is>
       </c>
       <c r="U4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>400.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="W4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -7467,21 +10524,21 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J5" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.8571428571428571</v>
+        <v>1.25</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -7490,14 +10547,14 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="R5" t="n">
@@ -7516,7 +10573,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="W5" t="n">
@@ -7546,17 +10603,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SLB_K._DOMINGUES</t>
+          <t>SLB_S._SOUSA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>292224</t>
+          <t>224422</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>K. Domingues</t>
+          <t>S. Sousa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -7565,27 +10622,27 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.7692307692307693</v>
       </c>
       <c r="M6" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="N6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -7595,7 +10652,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="R6" t="n">
@@ -7606,7 +10663,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="U6" t="n">
@@ -7614,7 +10671,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>500.0%</t>
         </is>
       </c>
       <c r="W6" t="n">
@@ -7622,7 +10679,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
     </row>
@@ -7644,17 +10701,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SLB_J._MENDES</t>
+          <t>SLB_K._DOMINGUES</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>217315</t>
+          <t>292224</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>J. Mendes</t>
+          <t>K. Domingues</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -7663,7 +10720,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I7" t="n">
         <v>4</v>
@@ -7673,14 +10730,14 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="M7" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="N7" t="n">
         <v>4</v>
@@ -7693,14 +10750,14 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="R7" t="n">
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -7708,15 +10765,15 @@
         </is>
       </c>
       <c r="U7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="W7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -7757,48 +10814,48 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.4</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="M8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="R8" t="n">
         <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -7806,7 +10863,7 @@
         </is>
       </c>
       <c r="U8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -7814,7 +10871,7 @@
         </is>
       </c>
       <c r="W8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -7859,21 +10916,21 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0.6</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -7882,14 +10939,14 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="P9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="R9" t="n">
@@ -7908,371 +10965,13 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="W9" t="n">
         <v>2</v>
       </c>
       <c r="X9" t="inlineStr">
-        <is>
-          <t>200.0%</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:X3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="23" customWidth="1" min="18" max="18"/>
-    <col width="28" customWidth="1" min="19" max="19"/>
-    <col width="25" customWidth="1" min="20" max="20"/>
-    <col width="32" customWidth="1" min="21" max="21"/>
-    <col width="29" customWidth="1" min="22" max="22"/>
-    <col width="38" customWidth="1" min="23" max="23"/>
-    <col width="35" customWidth="1" min="24" max="24"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>team_name</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>team_code</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>team_key</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>player_id</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>global_player_id</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>player_name</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>zone</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>attempts</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>made</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>points</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>fg_pct</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>pps</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>fg2a</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>fg2m</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>fg3a</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>fg3m</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>zone_share</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>eligible_zone_profile</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>player_zone_rank_by_volume</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>player_zone_rank_by_pct</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>player_zone_rank_by_volume_all</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>player_zone_rank_by_pct_all</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>player_zone_rank_by_volume_qualified</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>player_zone_rank_by_pct_qualified</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>SL Benfica</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>SLB</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>SLB</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>SLB_T._FILIPE</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>222661</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>T. Filipe</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J2" t="n">
-        <v>10</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="L2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M2" t="n">
-        <v>10</v>
-      </c>
-      <c r="N2" t="n">
-        <v>5</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="R2" t="n">
-        <v>1</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1</v>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="U2" t="n">
-        <v>1</v>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>SL Benfica</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>SLB</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>SLB</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>SLB_S._SOUSA</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>224422</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>S. Sousa</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>8</v>
-      </c>
-      <c r="I3" t="n">
-        <v>2</v>
-      </c>
-      <c r="J3" t="n">
-        <v>6</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>8</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>28.6%</t>
-        </is>
-      </c>
-      <c r="R3" t="n">
-        <v>1</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>200.0%</t>
-        </is>
-      </c>
-      <c r="U3" t="n">
-        <v>1</v>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>500.0%</t>
-        </is>
-      </c>
-      <c r="W3" t="n">
-        <v>1</v>
-      </c>
-      <c r="X3" t="inlineStr">
         <is>
           <t>200.0%</t>
         </is>
